--- a/teste/Plants_teste_chris.xlsx
+++ b/teste/Plants_teste_chris.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ead127730922d462/DOUTORADO/0.TESE/modelagem/modelo_bru/teste/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="89" documentId="13_ncr:1_{B62E733F-E2E4-4012-8470-C1B541D273FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D26A2378-E348-4C1E-9B03-5285ECF72DE8}"/>
+  <xr:revisionPtr revIDLastSave="90" documentId="13_ncr:1_{B62E733F-E2E4-4012-8470-C1B541D273FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22463E42-15A0-431C-A378-87BF56EEA715}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1683CF16-D6CE-428F-8B93-DD97FDAC2386}"/>
   </bookViews>
@@ -182,12 +182,13 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Planilha1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
+      <sheetData sheetId="0">
         <row r="2">
           <cell r="A2" t="str">
             <v>SBR00001</v>
